--- a/tablice_simpleks.xlsx
+++ b/tablice_simpleks.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prac608\Desktop\BO_KW1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB8025DB-4BC8-48E2-BB35-D0FBB1DC095D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE56531-6440-417C-B3D2-80E7BFEF02A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AD6F1831-D84A-46EA-B000-AAA6C86C7573}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{AD6F1831-D84A-46EA-B000-AAA6C86C7573}"/>
   </bookViews>
   <sheets>
     <sheet name="zadanie1" sheetId="1" r:id="rId1"/>
     <sheet name="zadanie2" sheetId="2" r:id="rId2"/>
+    <sheet name="metoda_macierz" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,8 +38,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="88">
   <si>
     <t>1.Zapis modelu</t>
   </si>
@@ -224,13 +247,91 @@
   </si>
   <si>
     <t>niewykorzytsany limit warunku 1</t>
+  </si>
+  <si>
+    <t>B2=</t>
+  </si>
+  <si>
+    <t>przy x3</t>
+  </si>
+  <si>
+    <t>B2^-1</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>B2^1*A=</t>
+  </si>
+  <si>
+    <t>=</t>
+  </si>
+  <si>
+    <t>B2^-1*b</t>
+  </si>
+  <si>
+    <t>Cb^t*bB2^-1*a</t>
+  </si>
+  <si>
+    <t>Cb^t*b=</t>
+  </si>
+  <si>
+    <t>Cb^t*b2^1</t>
+  </si>
+  <si>
+    <t>B3</t>
+  </si>
+  <si>
+    <t>z pierwitnej tablicy</t>
+  </si>
+  <si>
+    <t>B3^-1</t>
+  </si>
+  <si>
+    <t>B3^-1*A=</t>
+  </si>
+  <si>
+    <t>a=</t>
+  </si>
+  <si>
+    <t>B3^-1*b=</t>
+  </si>
+  <si>
+    <t>cb^t*B3^-1*A</t>
+  </si>
+  <si>
+    <t>cb^t*b3^-1</t>
+  </si>
+  <si>
+    <t>B4=</t>
+  </si>
+  <si>
+    <t>przyx2</t>
+  </si>
+  <si>
+    <t>B4^-1=</t>
+  </si>
+  <si>
+    <t>B4^-1*A=</t>
+  </si>
+  <si>
+    <t>B4^-1*b</t>
+  </si>
+  <si>
+    <t>cb^t*b4^-1*A</t>
+  </si>
+  <si>
+    <t>cb^t*b4^-1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -274,8 +375,18 @@
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -303,6 +414,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -360,7 +501,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -408,6 +549,25 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -568,6 +728,143 @@
         <a:xfrm>
           <a:off x="0" y="0"/>
           <a:ext cx="5915851" cy="1514686"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>198120</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>4609</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Obraz 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D8C11DA-C868-4300-8F3C-A58BD9A51A22}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="15240"/>
+          <a:ext cx="5074920" cy="2549689"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>381001</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>47919</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Obraz 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A47A8774-0B58-4DC5-B574-519B9B27587C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="381001" y="12870180"/>
+          <a:ext cx="4952999" cy="1259499"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>365760</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>333661</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>181229</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Obraz 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41773E33-1E75-488F-BE46-4C1D404C058A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="365760" y="18326100"/>
+          <a:ext cx="4844701" cy="1057529"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2451,7 +2748,7 @@
         <v>45</v>
       </c>
       <c r="J25" s="25">
-        <f t="shared" ref="I25:N25" si="6">SUMPRODUCT($F$22:$F$24,J22:J24)</f>
+        <f t="shared" ref="J25:N25" si="6">SUMPRODUCT($F$22:$F$24,J22:J24)</f>
         <v>15</v>
       </c>
       <c r="K25" s="28">
@@ -2789,6 +3086,1963 @@
       </c>
       <c r="H41" s="18">
         <v>5600</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3411A8DD-39E0-43D2-89B3-A780187B88CE}">
+  <dimension ref="I3:U108"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="3" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="3">
+        <v>32</v>
+      </c>
+      <c r="M3" s="3">
+        <v>24</v>
+      </c>
+      <c r="N3" s="16">
+        <v>48</v>
+      </c>
+      <c r="O3" s="3">
+        <v>0</v>
+      </c>
+      <c r="P3" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>0</v>
+      </c>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+    </row>
+    <row r="4" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J5" s="15">
+        <v>0</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="L5" s="6">
+        <v>2</v>
+      </c>
+      <c r="M5" s="6">
+        <v>2</v>
+      </c>
+      <c r="N5" s="30">
+        <v>5</v>
+      </c>
+      <c r="O5" s="36">
+        <v>1</v>
+      </c>
+      <c r="P5" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="36">
+        <v>0</v>
+      </c>
+      <c r="R5" s="34">
+        <v>40</v>
+      </c>
+      <c r="S5" s="15">
+        <f>R5/N5</f>
+        <v>8</v>
+      </c>
+      <c r="T5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="6">
+        <v>1</v>
+      </c>
+      <c r="M6" s="6">
+        <v>3</v>
+      </c>
+      <c r="N6" s="6">
+        <v>2</v>
+      </c>
+      <c r="O6" s="36">
+        <v>0</v>
+      </c>
+      <c r="P6" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="36">
+        <v>0</v>
+      </c>
+      <c r="R6" s="35">
+        <v>30</v>
+      </c>
+      <c r="S6" s="5">
+        <f>R6/N6</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="L7" s="6">
+        <v>3</v>
+      </c>
+      <c r="M7" s="6">
+        <v>1</v>
+      </c>
+      <c r="N7" s="6">
+        <v>3</v>
+      </c>
+      <c r="O7" s="36">
+        <v>0</v>
+      </c>
+      <c r="P7" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="36">
+        <v>1</v>
+      </c>
+      <c r="R7" s="35">
+        <v>30</v>
+      </c>
+      <c r="S7" s="5">
+        <f>R7/N7</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="K8" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" s="5">
+        <f>SUMPRODUCT($I$21:$I$23,L5:L7)</f>
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <f t="shared" ref="M8:R8" si="0">SUMPRODUCT($I$21:$I$23,M5:M7)</f>
+        <v>0</v>
+      </c>
+      <c r="N8" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O8" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="P8" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R8" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="K9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="L9" s="5">
+        <f>L3-L8</f>
+        <v>32</v>
+      </c>
+      <c r="M9" s="5">
+        <f t="shared" ref="M9:Q9" si="1">M3-M8</f>
+        <v>24</v>
+      </c>
+      <c r="N9" s="15">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="O9" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P9" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="N10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="K11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L11" t="s">
+        <v>32</v>
+      </c>
+      <c r="M11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J12" t="s">
+        <v>62</v>
+      </c>
+      <c r="K12" s="29">
+        <v>5</v>
+      </c>
+      <c r="L12" s="29">
+        <v>0</v>
+      </c>
+      <c r="M12" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="K13" s="29">
+        <v>2</v>
+      </c>
+      <c r="L13" s="29">
+        <v>1</v>
+      </c>
+      <c r="M13" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="K14" s="29">
+        <v>3</v>
+      </c>
+      <c r="L14" s="29">
+        <v>0</v>
+      </c>
+      <c r="M14" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J16" t="s">
+        <v>64</v>
+      </c>
+      <c r="K16" s="29" cm="1">
+        <f t="array" ref="K16:M18">MINVERSE(K12:M14)</f>
+        <v>0.2</v>
+      </c>
+      <c r="L16" s="29">
+        <v>0</v>
+      </c>
+      <c r="M16" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="K17" s="29">
+        <v>-0.4</v>
+      </c>
+      <c r="L17" s="29">
+        <v>1</v>
+      </c>
+      <c r="M17" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="K18" s="29">
+        <v>-0.6</v>
+      </c>
+      <c r="L18" s="29">
+        <v>0</v>
+      </c>
+      <c r="M18" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J20" t="s">
+        <v>67</v>
+      </c>
+      <c r="K20" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="L20" s="29">
+        <v>0</v>
+      </c>
+      <c r="M20" s="29">
+        <v>0</v>
+      </c>
+      <c r="N20" s="6">
+        <v>2</v>
+      </c>
+      <c r="O20" s="6">
+        <v>2</v>
+      </c>
+      <c r="P20" s="30">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="R20" s="2" cm="1">
+        <f t="array" ref="R20:T22">MMULT(_xlfn.ANCHORARRAY(K16),N20:P22)</f>
+        <v>0.4</v>
+      </c>
+      <c r="S20" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="T20" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="K21" s="29">
+        <v>-0.4</v>
+      </c>
+      <c r="L21" s="29">
+        <v>1</v>
+      </c>
+      <c r="M21" s="29">
+        <v>0</v>
+      </c>
+      <c r="N21" s="6">
+        <v>1</v>
+      </c>
+      <c r="O21" s="6">
+        <v>3</v>
+      </c>
+      <c r="P21" s="6">
+        <v>2</v>
+      </c>
+      <c r="R21" s="2">
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="S21" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="T21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="K22" s="29">
+        <v>-0.6</v>
+      </c>
+      <c r="L22" s="29">
+        <v>0</v>
+      </c>
+      <c r="M22" s="29">
+        <v>1</v>
+      </c>
+      <c r="N22" s="6">
+        <v>3</v>
+      </c>
+      <c r="O22" s="6">
+        <v>1</v>
+      </c>
+      <c r="P22" s="6">
+        <v>3</v>
+      </c>
+      <c r="R22" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="S22" s="2">
+        <v>-0.19999999999999996</v>
+      </c>
+      <c r="T22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J23" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="24" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="K24" s="29">
+        <v>0.2</v>
+      </c>
+      <c r="L24" s="29">
+        <v>0</v>
+      </c>
+      <c r="M24" s="29">
+        <v>0</v>
+      </c>
+      <c r="N24" s="32">
+        <v>40</v>
+      </c>
+      <c r="P24" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q24" s="33" cm="1">
+        <f t="array" ref="Q24:Q26">MMULT(K24:M26,N24:N26)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="K25" s="29">
+        <v>-0.4</v>
+      </c>
+      <c r="L25" s="29">
+        <v>1</v>
+      </c>
+      <c r="M25" s="29">
+        <v>0</v>
+      </c>
+      <c r="N25" s="33">
+        <v>30</v>
+      </c>
+      <c r="Q25" s="33">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="K26" s="29">
+        <v>-0.6</v>
+      </c>
+      <c r="L26" s="29">
+        <v>0</v>
+      </c>
+      <c r="M26" s="29">
+        <v>1</v>
+      </c>
+      <c r="N26" s="32">
+        <v>30</v>
+      </c>
+      <c r="Q26" s="33">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J28" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="K29" s="37">
+        <v>48</v>
+      </c>
+      <c r="L29" s="37">
+        <v>0</v>
+      </c>
+      <c r="M29" s="37">
+        <v>0</v>
+      </c>
+      <c r="N29" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="O29" s="6">
+        <v>0</v>
+      </c>
+      <c r="P29" s="30">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="R29" s="38" cm="1">
+        <f t="array" ref="R29:T29">MMULT(K29:M29,N29:P31)</f>
+        <v>9.6000000000000014</v>
+      </c>
+      <c r="S29" s="38">
+        <v>0</v>
+      </c>
+      <c r="T29" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="N30" s="6">
+        <v>-0.4</v>
+      </c>
+      <c r="O30" s="6">
+        <v>1</v>
+      </c>
+      <c r="P30" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="N31" s="6">
+        <v>-0.6</v>
+      </c>
+      <c r="O31" s="6">
+        <v>0</v>
+      </c>
+      <c r="P31" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J33" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="34" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="K34" s="37">
+        <v>48</v>
+      </c>
+      <c r="L34" s="37">
+        <v>0</v>
+      </c>
+      <c r="M34" s="37">
+        <v>0</v>
+      </c>
+      <c r="N34" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="O34" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="P34" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="R34" s="38" cm="1">
+        <f t="array" ref="R34:T34">MMULT(K34:M34,N34:P36)</f>
+        <v>19.200000000000003</v>
+      </c>
+      <c r="S34" s="38">
+        <v>19.200000000000003</v>
+      </c>
+      <c r="T34" s="38">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="N35" s="2">
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="O35" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="P35" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="N36" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="O36" s="2">
+        <v>-0.19999999999999996</v>
+      </c>
+      <c r="P36" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="S37" t="s">
+        <v>71</v>
+      </c>
+      <c r="T37" s="39" cm="1">
+        <f t="array" ref="T37">MMULT(_xlfn.ANCHORARRAY(R29),N24:N26)</f>
+        <v>384.00000000000006</v>
+      </c>
+    </row>
+    <row r="39" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J39" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L39" s="3">
+        <v>32</v>
+      </c>
+      <c r="M39" s="3">
+        <v>24</v>
+      </c>
+      <c r="N39" s="16">
+        <v>48</v>
+      </c>
+      <c r="O39" s="3">
+        <v>0</v>
+      </c>
+      <c r="P39" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="3">
+        <v>0</v>
+      </c>
+      <c r="R39" s="1"/>
+      <c r="S39" s="1"/>
+    </row>
+    <row r="40" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J40" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K40" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L40" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M40" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="O40" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="P40" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q40" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="R40" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="S40" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J41" s="15">
+        <v>48</v>
+      </c>
+      <c r="K41" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="L41" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="M41" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="N41" s="40">
+        <v>1</v>
+      </c>
+      <c r="O41" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="P41" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="36">
+        <v>0</v>
+      </c>
+      <c r="R41" s="34">
+        <v>8</v>
+      </c>
+      <c r="S41" s="15">
+        <f>R41/L41</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J42" s="5">
+        <v>0</v>
+      </c>
+      <c r="K42" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L42" s="6">
+        <v>0.19999999999999996</v>
+      </c>
+      <c r="M42" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="N42" s="6">
+        <v>0</v>
+      </c>
+      <c r="O42" s="36">
+        <v>-0.4</v>
+      </c>
+      <c r="P42" s="36">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="36">
+        <v>0</v>
+      </c>
+      <c r="R42" s="35">
+        <v>14</v>
+      </c>
+      <c r="S42" s="15">
+        <f t="shared" ref="S42:S43" si="2">R42/L42</f>
+        <v>70.000000000000014</v>
+      </c>
+    </row>
+    <row r="43" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="J43" s="5">
+        <v>0</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="L43" s="6">
+        <v>1.8</v>
+      </c>
+      <c r="M43" s="6">
+        <v>-0.19999999999999996</v>
+      </c>
+      <c r="N43" s="6">
+        <v>0</v>
+      </c>
+      <c r="O43" s="36">
+        <v>-0.6</v>
+      </c>
+      <c r="P43" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="36">
+        <v>1</v>
+      </c>
+      <c r="R43" s="35">
+        <v>6</v>
+      </c>
+      <c r="S43" s="15">
+        <f t="shared" si="2"/>
+        <v>3.333333333333333</v>
+      </c>
+      <c r="T43" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="44" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="K44" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="L44" s="38">
+        <v>19.200000000000003</v>
+      </c>
+      <c r="M44" s="38">
+        <v>19.200000000000003</v>
+      </c>
+      <c r="N44" s="38">
+        <v>48</v>
+      </c>
+      <c r="O44" s="5">
+        <v>9.6000000000000014</v>
+      </c>
+      <c r="P44" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="5">
+        <v>0</v>
+      </c>
+      <c r="R44" s="12">
+        <f>T37</f>
+        <v>384.00000000000006</v>
+      </c>
+    </row>
+    <row r="45" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="K45" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="L45" s="5">
+        <f>L39-L44</f>
+        <v>12.799999999999997</v>
+      </c>
+      <c r="M45" s="5">
+        <f t="shared" ref="M45:Q45" si="3">M39-M44</f>
+        <v>4.7999999999999972</v>
+      </c>
+      <c r="N45" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O45" s="5">
+        <f t="shared" si="3"/>
+        <v>-9.6000000000000014</v>
+      </c>
+      <c r="P45" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q45" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="L46" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="48" spans="10:20" x14ac:dyDescent="0.3">
+      <c r="K48" t="s">
+        <v>30</v>
+      </c>
+      <c r="L48" t="s">
+        <v>32</v>
+      </c>
+      <c r="M48" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="49" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="J49" t="s">
+        <v>73</v>
+      </c>
+      <c r="K49" s="18">
+        <v>5</v>
+      </c>
+      <c r="L49" s="18">
+        <v>0</v>
+      </c>
+      <c r="M49" s="18">
+        <v>2</v>
+      </c>
+      <c r="O49" t="s">
+        <v>75</v>
+      </c>
+      <c r="P49" s="18" cm="1">
+        <f t="array" ref="P49:R51">MINVERSE(K49:M51)</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="Q49" s="18">
+        <v>0</v>
+      </c>
+      <c r="R49" s="18">
+        <v>-0.22222222222222224</v>
+      </c>
+    </row>
+    <row r="50" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I50" t="s">
+        <v>74</v>
+      </c>
+      <c r="K50" s="18">
+        <v>2</v>
+      </c>
+      <c r="L50" s="18">
+        <v>1</v>
+      </c>
+      <c r="M50" s="18">
+        <v>1</v>
+      </c>
+      <c r="P50" s="18">
+        <v>-0.33333333333333337</v>
+      </c>
+      <c r="Q50" s="18">
+        <v>1</v>
+      </c>
+      <c r="R50" s="18">
+        <v>-0.11111111111111109</v>
+      </c>
+    </row>
+    <row r="51" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="K51" s="18">
+        <v>3</v>
+      </c>
+      <c r="L51" s="18">
+        <v>0</v>
+      </c>
+      <c r="M51" s="18">
+        <v>3</v>
+      </c>
+      <c r="P51" s="18">
+        <v>-0.33333333333333331</v>
+      </c>
+      <c r="Q51" s="18">
+        <v>0</v>
+      </c>
+      <c r="R51" s="18">
+        <v>0.55555555555555558</v>
+      </c>
+    </row>
+    <row r="53" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="I53" t="s">
+        <v>77</v>
+      </c>
+      <c r="J53" t="s">
+        <v>76</v>
+      </c>
+      <c r="K53" s="18">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="L53" s="18">
+        <v>0</v>
+      </c>
+      <c r="M53" s="18">
+        <v>-0.22222222222222224</v>
+      </c>
+      <c r="N53" s="2">
+        <v>2</v>
+      </c>
+      <c r="O53" s="2">
+        <v>2</v>
+      </c>
+      <c r="P53" s="2">
+        <v>5</v>
+      </c>
+      <c r="Q53" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="R53" s="41" cm="1">
+        <f t="array" ref="R53:T55">MMULT(K53:M55,N53:P55)</f>
+        <v>-1.1102230246251565E-16</v>
+      </c>
+      <c r="S53" s="41">
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="T53" s="41">
+        <v>0.99999999999999978</v>
+      </c>
+    </row>
+    <row r="54" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="K54" s="18">
+        <v>-0.33333333333333337</v>
+      </c>
+      <c r="L54" s="18">
+        <v>1</v>
+      </c>
+      <c r="M54" s="18">
+        <v>-0.11111111111111109</v>
+      </c>
+      <c r="N54" s="2">
+        <v>1</v>
+      </c>
+      <c r="O54" s="2">
+        <v>3</v>
+      </c>
+      <c r="P54" s="2">
+        <v>2</v>
+      </c>
+      <c r="R54" s="41">
+        <v>0</v>
+      </c>
+      <c r="S54" s="41">
+        <v>2.2222222222222219</v>
+      </c>
+      <c r="T54" s="41">
+        <v>-2.2204460492503131E-16</v>
+      </c>
+    </row>
+    <row r="55" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="K55" s="18">
+        <v>-0.33333333333333331</v>
+      </c>
+      <c r="L55" s="18">
+        <v>0</v>
+      </c>
+      <c r="M55" s="18">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="N55" s="2">
+        <v>3</v>
+      </c>
+      <c r="O55" s="2">
+        <v>1</v>
+      </c>
+      <c r="P55" s="2">
+        <v>3</v>
+      </c>
+      <c r="R55" s="41">
+        <v>1</v>
+      </c>
+      <c r="S55" s="41">
+        <v>-0.11111111111111105</v>
+      </c>
+      <c r="T55" s="41">
+        <v>2.2204460492503131E-16</v>
+      </c>
+    </row>
+    <row r="58" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="J58" t="s">
+        <v>78</v>
+      </c>
+      <c r="K58" s="44">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="L58" s="44">
+        <v>0</v>
+      </c>
+      <c r="M58" s="44">
+        <v>-0.22222222222222224</v>
+      </c>
+      <c r="N58" s="42">
+        <v>40</v>
+      </c>
+      <c r="O58" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="P58" s="43" cm="1">
+        <f t="array" ref="P58:P60">MMULT(K58:M60,N58:N60)</f>
+        <v>6.6666666666666652</v>
+      </c>
+    </row>
+    <row r="59" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="K59" s="44">
+        <v>-0.33333333333333337</v>
+      </c>
+      <c r="L59" s="44">
+        <v>1</v>
+      </c>
+      <c r="M59" s="44">
+        <v>-0.11111111111111109</v>
+      </c>
+      <c r="N59" s="42">
+        <v>30</v>
+      </c>
+      <c r="P59" s="43">
+        <v>13.333333333333332</v>
+      </c>
+    </row>
+    <row r="60" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="K60" s="44">
+        <v>-0.33333333333333331</v>
+      </c>
+      <c r="L60" s="44">
+        <v>0</v>
+      </c>
+      <c r="M60" s="44">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="N60" s="42">
+        <v>30</v>
+      </c>
+      <c r="P60" s="43">
+        <v>3.3333333333333357</v>
+      </c>
+    </row>
+    <row r="63" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="J63" t="s">
+        <v>79</v>
+      </c>
+      <c r="L63" s="45">
+        <v>48</v>
+      </c>
+      <c r="M63" s="45">
+        <v>0</v>
+      </c>
+      <c r="N63" s="37">
+        <v>32</v>
+      </c>
+      <c r="O63" s="41">
+        <v>-1.1102230246251565E-16</v>
+      </c>
+      <c r="P63" s="41">
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="Q63" s="41">
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="R63" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="S63" s="38" cm="1">
+        <f t="array" ref="S63:U63">MMULT(L63:N63,O63:Q65)</f>
+        <v>31.999999999999993</v>
+      </c>
+      <c r="T63" s="38">
+        <v>17.777777777777779</v>
+      </c>
+      <c r="U63" s="38">
+        <v>47.999999999999993</v>
+      </c>
+    </row>
+    <row r="64" spans="9:21" x14ac:dyDescent="0.3">
+      <c r="O64" s="41">
+        <v>0</v>
+      </c>
+      <c r="P64" s="41">
+        <v>2.2222222222222219</v>
+      </c>
+      <c r="Q64" s="41">
+        <v>-2.2204460492503131E-16</v>
+      </c>
+    </row>
+    <row r="65" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="O65" s="41">
+        <v>1</v>
+      </c>
+      <c r="P65" s="41">
+        <v>-0.11111111111111105</v>
+      </c>
+      <c r="Q65" s="41">
+        <v>2.2204460492503131E-16</v>
+      </c>
+    </row>
+    <row r="67" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="J67" t="s">
+        <v>80</v>
+      </c>
+      <c r="L67" s="45">
+        <v>48</v>
+      </c>
+      <c r="M67" s="45">
+        <v>0</v>
+      </c>
+      <c r="N67" s="37">
+        <v>32</v>
+      </c>
+      <c r="O67" s="44">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="P67" s="44">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="44">
+        <v>-0.22222222222222224</v>
+      </c>
+      <c r="R67" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="S67" s="38" cm="1">
+        <f t="array" ref="S67:U67">MMULT(L67:N67,O67:Q69)</f>
+        <v>5.3333333333333339</v>
+      </c>
+      <c r="T67" s="38">
+        <v>0</v>
+      </c>
+      <c r="U67" s="38">
+        <v>7.1111111111111107</v>
+      </c>
+    </row>
+    <row r="68" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="O68" s="44">
+        <v>-0.33333333333333337</v>
+      </c>
+      <c r="P68" s="44">
+        <v>1</v>
+      </c>
+      <c r="Q68" s="44">
+        <v>-0.11111111111111109</v>
+      </c>
+    </row>
+    <row r="69" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="O69" s="44">
+        <v>-0.33333333333333331</v>
+      </c>
+      <c r="P69" s="44">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="44">
+        <v>0.55555555555555558</v>
+      </c>
+    </row>
+    <row r="72" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="J72" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L72" s="3">
+        <v>32</v>
+      </c>
+      <c r="M72" s="3">
+        <v>24</v>
+      </c>
+      <c r="N72" s="16">
+        <v>48</v>
+      </c>
+      <c r="O72" s="3">
+        <v>0</v>
+      </c>
+      <c r="P72" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="3">
+        <v>0</v>
+      </c>
+      <c r="R72" s="1"/>
+      <c r="S72" s="1"/>
+    </row>
+    <row r="73" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="J73" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K73" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L73" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M73" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N73" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="O73" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="P73" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q73" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="R73" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="S73" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="74" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="J74" s="15">
+        <v>48</v>
+      </c>
+      <c r="K74" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="L74" s="6">
+        <v>-1.1102230246251565E-16</v>
+      </c>
+      <c r="M74" s="6">
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="N74" s="40">
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="O74" s="19">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="P74" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="19">
+        <v>-0.22222222222222224</v>
+      </c>
+      <c r="R74" s="46">
+        <v>6.6666666666666652</v>
+      </c>
+      <c r="S74" s="15">
+        <f>R74/M74</f>
+        <v>14.999999999999998</v>
+      </c>
+    </row>
+    <row r="75" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="J75" s="5">
+        <v>0</v>
+      </c>
+      <c r="K75" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L75" s="6">
+        <v>0</v>
+      </c>
+      <c r="M75" s="6">
+        <v>2.2222222222222219</v>
+      </c>
+      <c r="N75" s="6">
+        <v>-2.2204460492503131E-16</v>
+      </c>
+      <c r="O75" s="19">
+        <v>-0.33333333333333337</v>
+      </c>
+      <c r="P75" s="19">
+        <v>1</v>
+      </c>
+      <c r="Q75" s="19">
+        <v>-0.11111111111111109</v>
+      </c>
+      <c r="R75" s="47">
+        <v>13.333333333333332</v>
+      </c>
+      <c r="S75" s="15">
+        <f t="shared" ref="S75:S76" si="4">R75/M75</f>
+        <v>6</v>
+      </c>
+      <c r="T75" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="76" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="J76" s="5">
+        <v>32</v>
+      </c>
+      <c r="K76" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L76" s="6">
+        <v>1</v>
+      </c>
+      <c r="M76" s="6">
+        <v>-0.11111111111111105</v>
+      </c>
+      <c r="N76" s="6">
+        <v>2.2204460492503131E-16</v>
+      </c>
+      <c r="O76" s="19">
+        <v>-0.33333333333333331</v>
+      </c>
+      <c r="P76" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="19">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="R76" s="47">
+        <v>3.3333333333333357</v>
+      </c>
+      <c r="S76" s="15">
+        <f t="shared" si="4"/>
+        <v>-30.000000000000039</v>
+      </c>
+    </row>
+    <row r="77" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="K77" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="L77" s="38">
+        <v>31.999999999999993</v>
+      </c>
+      <c r="M77" s="38">
+        <v>17.777777777777779</v>
+      </c>
+      <c r="N77" s="38">
+        <v>47.999999999999993</v>
+      </c>
+      <c r="O77" s="38">
+        <v>5.3333333333333339</v>
+      </c>
+      <c r="P77" s="38">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="38">
+        <v>7.1111111111111107</v>
+      </c>
+      <c r="R77" s="12" cm="1">
+        <f t="array" ref="R77">MMULT(L67:N67,_xlfn.ANCHORARRAY(P58))</f>
+        <v>426.66666666666669</v>
+      </c>
+    </row>
+    <row r="78" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="K78" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="L78" s="5">
+        <f>L72-L77</f>
+        <v>0</v>
+      </c>
+      <c r="M78" s="5">
+        <f t="shared" ref="M78" si="5">M72-M77</f>
+        <v>6.2222222222222214</v>
+      </c>
+      <c r="N78" s="5">
+        <f t="shared" ref="N78" si="6">N72-N77</f>
+        <v>0</v>
+      </c>
+      <c r="O78" s="5">
+        <f t="shared" ref="O78" si="7">O72-O77</f>
+        <v>-5.3333333333333339</v>
+      </c>
+      <c r="P78" s="5">
+        <f t="shared" ref="P78" si="8">P72-P77</f>
+        <v>0</v>
+      </c>
+      <c r="Q78" s="5">
+        <f t="shared" ref="Q78" si="9">Q72-Q77</f>
+        <v>-7.1111111111111107</v>
+      </c>
+    </row>
+    <row r="79" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="M79" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="81" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="K81" t="s">
+        <v>63</v>
+      </c>
+      <c r="L81" t="s">
+        <v>82</v>
+      </c>
+      <c r="M81" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="82" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="J82" t="s">
+        <v>81</v>
+      </c>
+      <c r="K82" s="19">
+        <v>5</v>
+      </c>
+      <c r="L82" s="19">
+        <v>2</v>
+      </c>
+      <c r="M82" s="19">
+        <v>2</v>
+      </c>
+      <c r="O82" t="s">
+        <v>83</v>
+      </c>
+      <c r="P82" s="18" cm="1">
+        <f t="array" ref="P82:R84">MINVERSE(K82:M84)</f>
+        <v>0.4</v>
+      </c>
+      <c r="Q82" s="18">
+        <v>-0.19999999999999998</v>
+      </c>
+      <c r="R82" s="18">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="83" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="K83" s="19">
+        <v>2</v>
+      </c>
+      <c r="L83" s="19">
+        <v>3</v>
+      </c>
+      <c r="M83" s="19">
+        <v>1</v>
+      </c>
+      <c r="P83" s="18">
+        <v>-0.15</v>
+      </c>
+      <c r="Q83" s="18">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="R83" s="18">
+        <v>-4.9999999999999989E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="K84" s="19">
+        <v>3</v>
+      </c>
+      <c r="L84" s="19">
+        <v>1</v>
+      </c>
+      <c r="M84" s="19">
+        <v>3</v>
+      </c>
+      <c r="P84" s="18">
+        <v>-0.35000000000000003</v>
+      </c>
+      <c r="Q84" s="18">
+        <v>4.9999999999999989E-2</v>
+      </c>
+      <c r="R84" s="18">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="87" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="J87" t="s">
+        <v>84</v>
+      </c>
+      <c r="K87" s="18">
+        <v>0.4</v>
+      </c>
+      <c r="L87" s="18">
+        <v>-0.19999999999999998</v>
+      </c>
+      <c r="M87" s="18">
+        <v>-0.2</v>
+      </c>
+      <c r="N87" s="2">
+        <v>2</v>
+      </c>
+      <c r="O87" s="2">
+        <v>2</v>
+      </c>
+      <c r="P87" s="2">
+        <v>5</v>
+      </c>
+      <c r="Q87" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="R87" s="41" cm="1">
+        <f t="array" ref="R87:T89">MMULT(K87:M89,N87:P89)</f>
+        <v>0</v>
+      </c>
+      <c r="S87" s="41">
+        <v>5.5511151231257827E-17</v>
+      </c>
+      <c r="T87" s="41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="K88" s="18">
+        <v>-0.15</v>
+      </c>
+      <c r="L88" s="18">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="M88" s="18">
+        <v>-4.9999999999999989E-2</v>
+      </c>
+      <c r="N88" s="2">
+        <v>1</v>
+      </c>
+      <c r="O88" s="2">
+        <v>3</v>
+      </c>
+      <c r="P88" s="2">
+        <v>2</v>
+      </c>
+      <c r="R88" s="41">
+        <v>0</v>
+      </c>
+      <c r="S88" s="41">
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="T88" s="41">
+        <v>-5.5511151231257827E-17</v>
+      </c>
+    </row>
+    <row r="89" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="K89" s="18">
+        <v>-0.35000000000000003</v>
+      </c>
+      <c r="L89" s="18">
+        <v>4.9999999999999989E-2</v>
+      </c>
+      <c r="M89" s="18">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="N89" s="2">
+        <v>3</v>
+      </c>
+      <c r="O89" s="2">
+        <v>1</v>
+      </c>
+      <c r="P89" s="2">
+        <v>3</v>
+      </c>
+      <c r="R89" s="41">
+        <v>1</v>
+      </c>
+      <c r="S89" s="41">
+        <v>0</v>
+      </c>
+      <c r="T89" s="41">
+        <v>-2.2204460492503131E-16</v>
+      </c>
+    </row>
+    <row r="91" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="J91" t="s">
+        <v>85</v>
+      </c>
+      <c r="K91" s="18">
+        <v>0.4</v>
+      </c>
+      <c r="L91" s="18">
+        <v>-0.19999999999999998</v>
+      </c>
+      <c r="M91" s="18">
+        <v>-0.2</v>
+      </c>
+      <c r="N91" s="42">
+        <v>40</v>
+      </c>
+      <c r="O91" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="P91" s="42" cm="1">
+        <f t="array" ref="P91:P93">MMULT(K91:M93,N91:N93)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="K92" s="18">
+        <v>-0.15</v>
+      </c>
+      <c r="L92" s="18">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="M92" s="18">
+        <v>-4.9999999999999989E-2</v>
+      </c>
+      <c r="N92" s="42">
+        <v>30</v>
+      </c>
+      <c r="P92" s="42">
+        <v>5.9999999999999982</v>
+      </c>
+    </row>
+    <row r="93" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="K93" s="18">
+        <v>-0.35000000000000003</v>
+      </c>
+      <c r="L93" s="18">
+        <v>4.9999999999999989E-2</v>
+      </c>
+      <c r="M93" s="18">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="N93" s="42">
+        <v>30</v>
+      </c>
+      <c r="P93" s="42">
+        <v>3.9999999999999982</v>
+      </c>
+    </row>
+    <row r="95" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="J95" t="s">
+        <v>86</v>
+      </c>
+      <c r="L95" s="37">
+        <v>48</v>
+      </c>
+      <c r="M95" s="37">
+        <v>24</v>
+      </c>
+      <c r="N95" s="37">
+        <v>32</v>
+      </c>
+      <c r="O95" s="41">
+        <v>0</v>
+      </c>
+      <c r="P95" s="41">
+        <v>5.5511151231257827E-17</v>
+      </c>
+      <c r="Q95" s="41">
+        <v>1</v>
+      </c>
+      <c r="R95" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="S95" s="38" cm="1">
+        <f t="array" ref="S95:U95">MMULT(L95:N95,O95:Q97)</f>
+        <v>32</v>
+      </c>
+      <c r="T95" s="38">
+        <v>23.999999999999996</v>
+      </c>
+      <c r="U95" s="38">
+        <v>47.999999999999993</v>
+      </c>
+    </row>
+    <row r="96" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="O96" s="41">
+        <v>0</v>
+      </c>
+      <c r="P96" s="41">
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="Q96" s="41">
+        <v>-5.5511151231257827E-17</v>
+      </c>
+    </row>
+    <row r="97" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="O97" s="41">
+        <v>1</v>
+      </c>
+      <c r="P97" s="41">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="41">
+        <v>-2.2204460492503131E-16</v>
+      </c>
+    </row>
+    <row r="98" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="J98" t="s">
+        <v>87</v>
+      </c>
+      <c r="L98" s="37">
+        <v>48</v>
+      </c>
+      <c r="M98" s="37">
+        <v>24</v>
+      </c>
+      <c r="N98" s="37">
+        <v>32</v>
+      </c>
+      <c r="O98" s="18">
+        <v>0.4</v>
+      </c>
+      <c r="P98" s="18">
+        <v>-0.19999999999999998</v>
+      </c>
+      <c r="Q98" s="18">
+        <v>-0.2</v>
+      </c>
+      <c r="R98" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="S98" s="38" cm="1">
+        <f t="array" ref="S98:U98">MMULT(L98:N98,O98:Q100)</f>
+        <v>4.4000000000000021</v>
+      </c>
+      <c r="T98" s="38">
+        <v>2.7999999999999989</v>
+      </c>
+      <c r="U98" s="38">
+        <v>6.8000000000000007</v>
+      </c>
+    </row>
+    <row r="99" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="O99" s="18">
+        <v>-0.15</v>
+      </c>
+      <c r="P99" s="18">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="Q99" s="18">
+        <v>-4.9999999999999989E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="O100" s="18">
+        <v>-0.35000000000000003</v>
+      </c>
+      <c r="P100" s="18">
+        <v>4.9999999999999989E-2</v>
+      </c>
+      <c r="Q100" s="18">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="102" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="J102" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L102" s="3">
+        <v>32</v>
+      </c>
+      <c r="M102" s="3">
+        <v>24</v>
+      </c>
+      <c r="N102" s="16">
+        <v>48</v>
+      </c>
+      <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="1"/>
+      <c r="S102" s="1"/>
+    </row>
+    <row r="103" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="J103" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K103" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L103" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M103" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N103" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="O103" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="P103" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q103" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="R103" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="S103" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="104" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="J104" s="15">
+        <v>48</v>
+      </c>
+      <c r="K104" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="L104" s="41">
+        <v>0</v>
+      </c>
+      <c r="M104" s="41">
+        <v>5.5511151231257827E-17</v>
+      </c>
+      <c r="N104" s="41">
+        <v>1</v>
+      </c>
+      <c r="O104" s="19">
+        <v>0.4</v>
+      </c>
+      <c r="P104" s="19">
+        <v>-0.19999999999999998</v>
+      </c>
+      <c r="Q104" s="19">
+        <v>-0.2</v>
+      </c>
+      <c r="R104" s="46">
+        <v>4</v>
+      </c>
+      <c r="S104" s="15"/>
+    </row>
+    <row r="105" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="J105" s="5">
+        <v>0</v>
+      </c>
+      <c r="K105" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L105" s="41">
+        <v>0</v>
+      </c>
+      <c r="M105" s="41">
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="N105" s="41">
+        <v>-5.5511151231257827E-17</v>
+      </c>
+      <c r="O105" s="19">
+        <v>-0.15</v>
+      </c>
+      <c r="P105" s="19">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="Q105" s="19">
+        <v>-4.9999999999999989E-2</v>
+      </c>
+      <c r="R105" s="47">
+        <v>5.9999999999999982</v>
+      </c>
+      <c r="S105" s="15"/>
+    </row>
+    <row r="106" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="J106" s="5">
+        <v>32</v>
+      </c>
+      <c r="K106" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L106" s="41">
+        <v>1</v>
+      </c>
+      <c r="M106" s="41">
+        <v>0</v>
+      </c>
+      <c r="N106" s="41">
+        <v>-2.2204460492503131E-16</v>
+      </c>
+      <c r="O106" s="19">
+        <v>-0.35000000000000003</v>
+      </c>
+      <c r="P106" s="19">
+        <v>4.9999999999999989E-2</v>
+      </c>
+      <c r="Q106" s="19">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="R106" s="47">
+        <v>3.9999999999999982</v>
+      </c>
+      <c r="S106" s="15"/>
+    </row>
+    <row r="107" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="K107" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="L107" s="38">
+        <v>32</v>
+      </c>
+      <c r="M107" s="38">
+        <v>23.999999999999996</v>
+      </c>
+      <c r="N107" s="38">
+        <v>47.999999999999993</v>
+      </c>
+      <c r="O107" s="38">
+        <v>4.4000000000000021</v>
+      </c>
+      <c r="P107" s="38">
+        <v>2.7999999999999989</v>
+      </c>
+      <c r="Q107" s="38">
+        <v>6.8000000000000007</v>
+      </c>
+      <c r="R107" s="12" cm="1">
+        <f t="array" ref="R107">MMULT(L98:N98,_xlfn.ANCHORARRAY(P91))</f>
+        <v>463.99999999999989</v>
+      </c>
+    </row>
+    <row r="108" spans="10:21" x14ac:dyDescent="0.3">
+      <c r="K108" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="L108" s="5">
+        <f>L102-L107</f>
+        <v>0</v>
+      </c>
+      <c r="M108" s="5">
+        <f t="shared" ref="M108" si="10">M102-M107</f>
+        <v>0</v>
+      </c>
+      <c r="N108" s="5">
+        <f t="shared" ref="N108" si="11">N102-N107</f>
+        <v>0</v>
+      </c>
+      <c r="O108" s="5">
+        <f t="shared" ref="O108" si="12">O102-O107</f>
+        <v>-4.4000000000000021</v>
+      </c>
+      <c r="P108" s="5">
+        <f t="shared" ref="P108" si="13">P102-P107</f>
+        <v>-2.7999999999999989</v>
+      </c>
+      <c r="Q108" s="5">
+        <f t="shared" ref="Q108" si="14">Q102-Q107</f>
+        <v>-6.8000000000000007</v>
       </c>
     </row>
   </sheetData>
